--- a/apps/configurador-servicios/catalog/Catalogo_Tecnico_Servicios_ISM_Developer_v2_3_Simplificado_LIMPIO.xlsx
+++ b/apps/configurador-servicios/catalog/Catalogo_Tecnico_Servicios_ISM_Developer_v2_3_Simplificado_LIMPIO.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" r:id="R8efb857a5e2a4843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros" sheetId="2" r:id="R136ee76639cb4a08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" r:id="R7cb92b3cbc85453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo Maestro" sheetId="4" r:id="R75a869fd37974621"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desarrollo" sheetId="5" r:id="R9ae34bfcf89b4dce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento" sheetId="6" r:id="R1a874035ead24f23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoreo" sheetId="7" r:id="R2feb6359462448aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuidad" sheetId="8" r:id="R22cbff5aa95e41c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ciberseguridad" sheetId="9" r:id="R00d217e7e4014a8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soporte" sheetId="10" r:id="Re5469ee939384395"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculo Final" sheetId="11" r:id="Rd59c395bdd9c4719"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion HH" sheetId="12" r:id="Rd461f3afed4245c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" r:id="R85eefca9bf354e85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros" sheetId="2" r:id="R2c9fec03614b4348"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" r:id="Rc0a87b84073747a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo Maestro" sheetId="4" r:id="Rd2ec5d048b2647ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desarrollo" sheetId="5" r:id="R427d985f25f944b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento" sheetId="6" r:id="R3ac1558f18c544dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoreo" sheetId="7" r:id="R4599a35b3d594ca4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuidad" sheetId="8" r:id="R6daddeb555bf4704"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ciberseguridad" sheetId="9" r:id="Rd62f96f559be4973"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soporte" sheetId="10" r:id="Rab916ef6950042f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculo Final" sheetId="11" r:id="R1e8babc3d6244a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion HH" sheetId="12" r:id="Rb2a09a96476f46c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -573,292 +573,292 @@
     <x:t xml:space="preserve">Sección estándar de contenido</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Sección</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye por unidad: título, texto, imagen/icono, tarjetas simples o bloque informativo y adaptación responsive.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye lógica avanzada, filtros ni contenido dinámico.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-010</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sección de servicios con tarjetas</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: tarjetas de servicios, iconos o imágenes, descripciones breves y CTA relacionado.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye catálogo transaccional, reservas ni cálculo dinámico de precios.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-011</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Galería o portafolio</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Opcional</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: grilla/slider, visualización de proyectos o trabajos, modal o navegación simple según alcance.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye carga masiva, edición de imágenes ni CMS complejo.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-012</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Testimonios o casos de éxito</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: tarjetas, autor, cargo/empresa cuando aplique y adaptación responsive.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye producción de testimonios ni validación legal de contenido.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-013</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Preguntas frecuentes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: acordeón o listado estructurado, estados y contenido entregado por cliente.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye redacción especializada ni base de conocimiento dinámica.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Conversión</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-014</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Formulario de contacto con envío por correo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Formulario</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: campos, validaciones, estados, consentimiento básico, endpoint o servicio de envío, plantilla simple de correo y prueba de entrega.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye CRM, automatizaciones complejas, adjuntos pesados ni flujos de aprobación.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-015</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Footer y cierre de navegación</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: datos de contacto, enlaces legales/útiles, redes cuando existan y estructura responsive.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye contenido legal redactado por ISM.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Página interna estándar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Página</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: estructura reutilizando navbar/footer, hero interno y bloques estándar de contenido.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye lógica transaccional ni diseño completamente único por página.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-005; WEB-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Integración ligera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-017</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Integración de WhatsApp</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Integración</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: enlace, mensaje inicial opcional, CTA y pruebas de funcionamiento.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye chatbot, API oficial ni automatización de conversaciones.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-018</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Integración de redes sociales</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: enlaces/iconos a redes definidas y verificación básica.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye gestión de redes, feeds dinámicos ni APIs sociales.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-019</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Integración de mapa o ubicación</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: mapa embebido o enlace de ubicación y prueba responsive.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye cálculo de rutas, geocodificación ni mapas personalizados.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Contenido</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-021</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Carga y formato inicial de contenidos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: carga, jerarquía, formato y ajustes menores sobre textos e imágenes entregados por el cliente.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye copywriting profesional, traducción ni producción masiva de contenido.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Calidad</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-022</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Validación responsive y compatibilidad final</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: revisión final en móvil, tablet y escritorio; navegación; desbordes; foco; estados básicos y navegadores definidos. El responsive se construye desde el inicio en cada componente.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye reconstruir componentes fuera de alcance.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-007; WEB-008; WEB-009; WEB-010; WEB-014; WEB-015</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-023</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SEO técnico inicial e indexabilidad</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: titles, descriptions, canonical, OG/social, sitemap, robots, revisión de indexabilidad y datos estructurados básicos cuando apliquen.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye estrategia SEO mensual, link building ni investigación avanzada de palabras clave.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Optimización</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Optimización técnica y accesibilidad básica</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: compresión/formato de imágenes, lazy loading, revisión de peso, semántica, contraste, foco, labels y navegación básica por teclado.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye auditoría WCAG formal ni optimización avanzada de Core Web Vitals.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-007:WEB-021</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Analítica</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-029</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Analítica básica</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: configuración de herramienta analítica acordada, evento/pageview básico y validación.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye dashboards BI ni estrategia de medición avanzada.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-030</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QA funcional y ciclo consolidado de correcciones</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: pruebas de navegación y formularios/acciones presentes, revisión de enlaces, un ciclo consolidado de observaciones y correcciones dentro del alcance.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye cambios de alcance, nuevas secciones ni rediseño posterior a aprobación.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Publicación</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-033</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">APP-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Levantamiento funcional, alcance y flujos principales</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: procesos actuales; actores; objetivos; historias/casos principales; criterios de aceptación; mapa de navegación; flujos y estados principales.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye documentación regulatoria extensa, BPMN formal completo ni consultoría de procesos independiente.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Arquitectura</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">APP-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Modelo de datos y persistencia base</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye: entidades, relaciones, restricciones, esquema inicial, migraciones base y criterios de integridad.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No incluye migración masiva de datos ni modelamiento analítico avanzado.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Seguridad</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">APP-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Diseño de roles y permisos</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Base incluido</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sección</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye por unidad: título, texto, imagen/icono, tarjetas simples o bloque informativo y adaptación responsive.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye lógica avanzada, filtros ni contenido dinámico.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-010</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sección de servicios con tarjetas</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: tarjetas de servicios, iconos o imágenes, descripciones breves y CTA relacionado.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye catálogo transaccional, reservas ni cálculo dinámico de precios.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-011</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Galería o portafolio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Opcional</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: grilla/slider, visualización de proyectos o trabajos, modal o navegación simple según alcance.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye carga masiva, edición de imágenes ni CMS complejo.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-012</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Testimonios o casos de éxito</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: tarjetas, autor, cargo/empresa cuando aplique y adaptación responsive.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye producción de testimonios ni validación legal de contenido.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-013</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Preguntas frecuentes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: acordeón o listado estructurado, estados y contenido entregado por cliente.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye redacción especializada ni base de conocimiento dinámica.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Conversión</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-014</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Formulario de contacto con envío por correo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Formulario</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: campos, validaciones, estados, consentimiento básico, endpoint o servicio de envío, plantilla simple de correo y prueba de entrega.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye CRM, automatizaciones complejas, adjuntos pesados ni flujos de aprobación.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-015</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Footer y cierre de navegación</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: datos de contacto, enlaces legales/útiles, redes cuando existan y estructura responsive.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye contenido legal redactado por ISM.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-016</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Página interna estándar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Página</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: estructura reutilizando navbar/footer, hero interno y bloques estándar de contenido.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye lógica transaccional ni diseño completamente único por página.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-005; WEB-007</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Integración ligera</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-017</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Integración de WhatsApp</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Integración</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: enlace, mensaje inicial opcional, CTA y pruebas de funcionamiento.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye chatbot, API oficial ni automatización de conversaciones.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-018</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Integración de redes sociales</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: enlaces/iconos a redes definidas y verificación básica.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye gestión de redes, feeds dinámicos ni APIs sociales.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-019</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Integración de mapa o ubicación</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: mapa embebido o enlace de ubicación y prueba responsive.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye cálculo de rutas, geocodificación ni mapas personalizados.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Contenido</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-021</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Carga y formato inicial de contenidos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: carga, jerarquía, formato y ajustes menores sobre textos e imágenes entregados por el cliente.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye copywriting profesional, traducción ni producción masiva de contenido.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Calidad</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-022</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Validación responsive y compatibilidad final</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: revisión final en móvil, tablet y escritorio; navegación; desbordes; foco; estados básicos y navegadores definidos. El responsive se construye desde el inicio en cada componente.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye reconstruir componentes fuera de alcance.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-007; WEB-008; WEB-009; WEB-010; WEB-014; WEB-015</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-023</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SEO técnico inicial e indexabilidad</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: titles, descriptions, canonical, OG/social, sitemap, robots, revisión de indexabilidad y datos estructurados básicos cuando apliquen.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye estrategia SEO mensual, link building ni investigación avanzada de palabras clave.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Optimización</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Optimización técnica y accesibilidad básica</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: compresión/formato de imágenes, lazy loading, revisión de peso, semántica, contraste, foco, labels y navegación básica por teclado.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye auditoría WCAG formal ni optimización avanzada de Core Web Vitals.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-007:WEB-021</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Analítica</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-029</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Analítica básica</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: configuración de herramienta analítica acordada, evento/pageview básico y validación.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye dashboards BI ni estrategia de medición avanzada.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-030</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QA funcional y ciclo consolidado de correcciones</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: pruebas de navegación y formularios/acciones presentes, revisión de enlaces, un ciclo consolidado de observaciones y correcciones dentro del alcance.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye cambios de alcance, nuevas secciones ni rediseño posterior a aprobación.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Publicación</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-033</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">APP-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Levantamiento funcional, alcance y flujos principales</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: procesos actuales; actores; objetivos; historias/casos principales; criterios de aceptación; mapa de navegación; flujos y estados principales.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye documentación regulatoria extensa, BPMN formal completo ni consultoría de procesos independiente.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arquitectura</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">APP-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Modelo de datos y persistencia base</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye: entidades, relaciones, restricciones, esquema inicial, migraciones base y criterios de integridad.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No incluye migración masiva de datos ni modelamiento analítico avanzado.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Seguridad</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">APP-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Diseño de roles y permisos</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Rol</x:t>
@@ -7401,11 +7401,11 @@
       </x:c>
       <x:c r="E6" s="21" t="n">
         <x:f>SUMPRODUCT(('Catalogo Maestro'!$B$6:$B$260=B6)*('Catalogo Maestro'!$G$6:$G$260&lt;&gt;"Opcional")*'Catalogo Maestro'!$I$6:$I$260*'Catalogo Maestro'!$J$6:$J$260)</x:f>
-        <x:v>18.3</x:v>
+        <x:v>13.299999999999999</x:v>
       </x:c>
       <x:c r="F6" s="21" t="n">
         <x:f>E6*Parametros!$B$9</x:f>
-        <x:v>12.81</x:v>
+        <x:v>9.309999999999999</x:v>
       </x:c>
       <x:c r="G6" s="10" t="s">
         <x:v>103</x:v>
@@ -8267,11 +8267,11 @@
       <x:c r="F10" s="7" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="G10" s="7" t="s">
+      <x:c r="G10" s="7" t="str">
+        <x:v>Opcional</x:v>
+      </x:c>
+      <x:c r="H10" s="7" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="H10" s="7" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="I10" s="47">
         <x:v>1</x:v>
@@ -8284,10 +8284,10 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="L10" s="7" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="M10" s="7" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="M10" s="7" t="s">
-        <x:v>187</x:v>
       </x:c>
       <x:c r="N10" s="7" t="s">
         <x:v>167</x:v>
@@ -8310,16 +8310,16 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="E11" s="7" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F11" s="7" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F11" s="7" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G11" s="7" t="s">
+      <x:c r="G11" s="7" t="str">
+        <x:v>Opcional</x:v>
+      </x:c>
+      <x:c r="H11" s="7" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="H11" s="7" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="I11" s="47">
         <x:v>1</x:v>
@@ -8332,10 +8332,10 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="L11" s="7" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="M11" s="7" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="M11" s="7" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="N11" s="7" t="s">
         <x:v>167</x:v>
@@ -8358,16 +8358,16 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="E12" s="7" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F12" s="7" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="F12" s="7" t="s">
+      <x:c r="G12" s="7" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="G12" s="7" t="s">
-        <x:v>194</x:v>
-      </x:c>
       <x:c r="H12" s="7" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="I12" s="47">
         <x:v>1</x:v>
@@ -8380,10 +8380,10 @@
         <x:v>1.0499999999999998</x:v>
       </x:c>
       <x:c r="L12" s="7" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="M12" s="7" t="s">
         <x:v>195</x:v>
-      </x:c>
-      <x:c r="M12" s="7" t="s">
-        <x:v>196</x:v>
       </x:c>
       <x:c r="N12" s="7" t="s">
         <x:v>167</x:v>
@@ -8406,16 +8406,16 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="E13" s="7" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F13" s="7" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="F13" s="7" t="s">
-        <x:v>198</x:v>
-      </x:c>
       <x:c r="G13" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H13" s="7" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="I13" s="47">
         <x:v>1</x:v>
@@ -8428,10 +8428,10 @@
         <x:v>1.0499999999999998</x:v>
       </x:c>
       <x:c r="L13" s="7" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M13" s="7" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="M13" s="7" t="s">
-        <x:v>200</x:v>
       </x:c>
       <x:c r="N13" s="7" t="s">
         <x:v>167</x:v>
@@ -8454,16 +8454,16 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="E14" s="7" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F14" s="7" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="F14" s="7" t="s">
-        <x:v>202</x:v>
-      </x:c>
       <x:c r="G14" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H14" s="7" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="I14" s="47">
         <x:v>1</x:v>
@@ -8476,10 +8476,10 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="L14" s="7" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="M14" s="7" t="s">
         <x:v>203</x:v>
-      </x:c>
-      <x:c r="M14" s="7" t="s">
-        <x:v>204</x:v>
       </x:c>
       <x:c r="N14" s="7" t="s">
         <x:v>167</x:v>
@@ -8499,19 +8499,19 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D15" s="7" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="E15" s="7" t="s">
+      <x:c r="F15" s="7" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="F15" s="7" t="s">
+      <x:c r="G15" s="7" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H15" s="7" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="G15" s="7" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H15" s="7" t="s">
-        <x:v>208</x:v>
       </x:c>
       <x:c r="I15" s="47">
         <x:v>1</x:v>
@@ -8524,10 +8524,10 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="L15" s="7" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="M15" s="7" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="M15" s="7" t="s">
-        <x:v>210</x:v>
       </x:c>
       <x:c r="N15" s="7" t="s">
         <x:v>167</x:v>
@@ -8550,10 +8550,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="E16" s="7" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F16" s="7" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="F16" s="7" t="s">
-        <x:v>212</x:v>
       </x:c>
       <x:c r="G16" s="7" t="s">
         <x:v>162</x:v>
@@ -8572,10 +8572,10 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="L16" s="7" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="M16" s="7" t="s">
         <x:v>213</x:v>
-      </x:c>
-      <x:c r="M16" s="7" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="N16" s="7" t="s">
         <x:v>167</x:v>
@@ -8598,16 +8598,16 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="E17" s="7" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F17" s="7" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="F17" s="7" t="s">
+      <x:c r="G17" s="7" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H17" s="7" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="G17" s="7" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H17" s="7" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="I17" s="47">
         <x:v>1</x:v>
@@ -8620,13 +8620,13 @@
         <x:v>1.0499999999999998</x:v>
       </x:c>
       <x:c r="L17" s="7" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="M17" s="7" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="M17" s="7" t="s">
+      <x:c r="N17" s="7" t="s">
         <x:v>219</x:v>
-      </x:c>
-      <x:c r="N17" s="7" t="s">
-        <x:v>220</x:v>
       </x:c>
       <x:c r="O17" s="12" t="s">
         <x:v>103</x:v>
@@ -8643,19 +8643,19 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D18" s="7" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="E18" s="7" t="s">
+      <x:c r="F18" s="7" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F18" s="7" t="s">
+      <x:c r="G18" s="7" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H18" s="7" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="G18" s="7" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H18" s="7" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="I18" s="47">
         <x:v>1</x:v>
@@ -8668,10 +8668,10 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="L18" s="7" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="M18" s="7" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="M18" s="7" t="s">
-        <x:v>226</x:v>
       </x:c>
       <x:c r="N18" s="7"/>
       <x:c r="O18" s="12" t="s">
@@ -8689,19 +8689,19 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D19" s="7" t="s">
-        <x:v>221</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E19" s="7" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F19" s="7" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="F19" s="7" t="s">
-        <x:v>228</x:v>
-      </x:c>
       <x:c r="G19" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H19" s="7" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I19" s="47">
         <x:v>1</x:v>
@@ -8714,10 +8714,10 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="L19" s="7" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="M19" s="7" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="M19" s="7" t="s">
-        <x:v>230</x:v>
       </x:c>
       <x:c r="N19" s="7"/>
       <x:c r="O19" s="12" t="s">
@@ -8735,19 +8735,19 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D20" s="7" t="s">
-        <x:v>221</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E20" s="7" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F20" s="7" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="F20" s="7" t="s">
-        <x:v>232</x:v>
-      </x:c>
       <x:c r="G20" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H20" s="7" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I20" s="47">
         <x:v>1</x:v>
@@ -8760,10 +8760,10 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="L20" s="7" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="M20" s="7" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="M20" s="7" t="s">
-        <x:v>234</x:v>
       </x:c>
       <x:c r="N20" s="7"/>
       <x:c r="O20" s="12" t="s">
@@ -8781,16 +8781,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D21" s="7" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="E21" s="7" t="s">
+      <x:c r="F21" s="7" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="F21" s="7" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="G21" s="7" t="s">
-        <x:v>184</x:v>
+      <x:c r="G21" s="7" t="str">
+        <x:v>Base obligatorio</x:v>
       </x:c>
       <x:c r="H21" s="7" t="s">
         <x:v>163</x:v>
@@ -8806,10 +8806,10 @@
         <x:v>0.84</x:v>
       </x:c>
       <x:c r="L21" s="7" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="M21" s="7" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="M21" s="7" t="s">
-        <x:v>239</x:v>
       </x:c>
       <x:c r="N21" s="7" t="s">
         <x:v>160</x:v>
@@ -8829,13 +8829,13 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D22" s="7" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="E22" s="7" t="s">
+      <x:c r="F22" s="7" t="s">
         <x:v>241</x:v>
-      </x:c>
-      <x:c r="F22" s="7" t="s">
-        <x:v>242</x:v>
       </x:c>
       <x:c r="G22" s="7" t="s">
         <x:v>162</x:v>
@@ -8854,13 +8854,13 @@
         <x:v>1.4</x:v>
       </x:c>
       <x:c r="L22" s="7" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="M22" s="7" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="M22" s="7" t="s">
+      <x:c r="N22" s="7" t="s">
         <x:v>244</x:v>
-      </x:c>
-      <x:c r="N22" s="7" t="s">
-        <x:v>245</x:v>
       </x:c>
       <x:c r="O22" s="12" t="s">
         <x:v>103</x:v>
@@ -8877,16 +8877,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D23" s="7" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="E23" s="7" t="s">
+      <x:c r="F23" s="7" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="F23" s="7" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="G23" s="7" t="s">
-        <x:v>184</x:v>
+      <x:c r="G23" s="7" t="str">
+        <x:v>Opcional</x:v>
       </x:c>
       <x:c r="H23" s="7" t="s">
         <x:v>163</x:v>
@@ -8902,10 +8902,10 @@
         <x:v>1.0499999999999998</x:v>
       </x:c>
       <x:c r="L23" s="7" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="M23" s="7" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="M23" s="7" t="s">
-        <x:v>250</x:v>
       </x:c>
       <x:c r="N23" s="7" t="s">
         <x:v>160</x:v>
@@ -8925,16 +8925,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D24" s="7" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="E24" s="7" t="s">
+      <x:c r="F24" s="7" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="F24" s="7" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="G24" s="7" t="s">
-        <x:v>184</x:v>
+      <x:c r="G24" s="7" t="str">
+        <x:v>Opcional</x:v>
       </x:c>
       <x:c r="H24" s="7" t="s">
         <x:v>163</x:v>
@@ -8950,13 +8950,13 @@
         <x:v>1.0499999999999998</x:v>
       </x:c>
       <x:c r="L24" s="7" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="M24" s="7" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="M24" s="7" t="s">
+      <x:c r="N24" s="7" t="s">
         <x:v>255</x:v>
-      </x:c>
-      <x:c r="N24" s="7" t="s">
-        <x:v>256</x:v>
       </x:c>
       <x:c r="O24" s="12" t="s">
         <x:v>103</x:v>
@@ -8973,16 +8973,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D25" s="7" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="E25" s="7" t="s">
+      <x:c r="F25" s="7" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="F25" s="7" t="s">
-        <x:v>259</x:v>
-      </x:c>
       <x:c r="G25" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H25" s="7" t="s">
         <x:v>163</x:v>
@@ -8998,10 +8998,10 @@
         <x:v>0.42</x:v>
       </x:c>
       <x:c r="L25" s="7" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="M25" s="7" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="M25" s="7" t="s">
-        <x:v>261</x:v>
       </x:c>
       <x:c r="N25" s="7"/>
       <x:c r="O25" s="12" t="s">
@@ -9019,13 +9019,13 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D26" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E26" s="7" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F26" s="7" t="s">
         <x:v>262</x:v>
-      </x:c>
-      <x:c r="F26" s="7" t="s">
-        <x:v>263</x:v>
       </x:c>
       <x:c r="G26" s="7" t="s">
         <x:v>162</x:v>
@@ -9044,13 +9044,13 @@
         <x:v>1.0499999999999998</x:v>
       </x:c>
       <x:c r="L26" s="7" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="M26" s="7" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="M26" s="7" t="s">
-        <x:v>265</x:v>
-      </x:c>
       <x:c r="N26" s="7" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="O26" s="12" t="s">
         <x:v>103</x:v>
@@ -9067,10 +9067,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D27" s="7" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="E27" s="7" t="s">
-        <x:v>267</x:v>
       </x:c>
       <x:c r="F27" s="7" t="str">
         <x:v>Publicación, SSL y entrega</x:v>
@@ -9098,7 +9098,7 @@
         <x:v>No incluye compra, renovación, configuración o migración de dominio/DNS ni costos de hosting/proveedores. El trabajo de dominio se selecciona por separado cuando corresponda.</x:v>
       </x:c>
       <x:c r="N27" s="7" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="O27" s="12" t="s">
         <x:v>103</x:v>
@@ -9118,10 +9118,10 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="E28" s="7" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="F28" s="7" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="F28" s="7" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="G28" s="7" t="s">
         <x:v>162</x:v>
@@ -9140,10 +9140,10 @@
         <x:v>1.0499999999999998</x:v>
       </x:c>
       <x:c r="L28" s="7" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="M28" s="7" t="s">
         <x:v>270</x:v>
-      </x:c>
-      <x:c r="M28" s="7" t="s">
-        <x:v>271</x:v>
       </x:c>
       <x:c r="N28" s="7"/>
       <x:c r="O28" s="12" t="s">
@@ -9161,13 +9161,13 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="D29" s="7" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="E29" s="7" t="s">
+      <x:c r="F29" s="7" t="s">
         <x:v>273</x:v>
-      </x:c>
-      <x:c r="F29" s="7" t="s">
-        <x:v>274</x:v>
       </x:c>
       <x:c r="G29" s="7" t="s">
         <x:v>162</x:v>
@@ -9186,13 +9186,13 @@
         <x:v>1.75</x:v>
       </x:c>
       <x:c r="L29" s="7" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="M29" s="7" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="M29" s="7" t="s">
-        <x:v>276</x:v>
-      </x:c>
       <x:c r="N29" s="7" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="O29" s="12" t="s">
         <x:v>103</x:v>
@@ -9209,16 +9209,16 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="D30" s="7" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="E30" s="7" t="s">
+      <x:c r="F30" s="7" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="F30" s="7" t="s">
+      <x:c r="G30" s="7" t="s">
         <x:v>279</x:v>
-      </x:c>
-      <x:c r="G30" s="7" t="s">
-        <x:v>184</x:v>
       </x:c>
       <x:c r="H30" s="7" t="s">
         <x:v>280</x:v>
@@ -9240,7 +9240,7 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="N30" s="7" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="O30" s="12" t="s">
         <x:v>103</x:v>
@@ -9257,7 +9257,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="D31" s="7" t="s">
-        <x:v>272</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E31" s="7" t="s">
         <x:v>283</x:v>
@@ -9288,7 +9288,7 @@
         <x:v>286</x:v>
       </x:c>
       <x:c r="N31" s="7" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="O31" s="12" t="s">
         <x:v>103</x:v>
@@ -9314,7 +9314,7 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="G32" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H32" s="7" t="s">
         <x:v>290</x:v>
@@ -9336,7 +9336,7 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="N32" s="7" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="O32" s="12" t="s">
         <x:v>103</x:v>
@@ -9410,7 +9410,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="G34" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H34" s="7" t="s">
         <x:v>290</x:v>
@@ -9458,7 +9458,7 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="G35" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H35" s="7" t="s">
         <x:v>306</x:v>
@@ -9480,7 +9480,7 @@
         <x:v>308</x:v>
       </x:c>
       <x:c r="N35" s="7" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="O35" s="12" t="s">
         <x:v>103</x:v>
@@ -9506,7 +9506,7 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="G36" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H36" s="7" t="s">
         <x:v>312</x:v>
@@ -9528,7 +9528,7 @@
         <x:v>314</x:v>
       </x:c>
       <x:c r="N36" s="7" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="O36" s="12" t="s">
         <x:v>103</x:v>
@@ -9545,7 +9545,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="D37" s="7" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E37" s="7" t="s">
         <x:v>315</x:v>
@@ -9593,7 +9593,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="D38" s="7" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E38" s="7" t="s">
         <x:v>321</x:v>
@@ -9602,7 +9602,7 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="G38" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H38" s="7" t="s">
         <x:v>280</x:v>
@@ -9650,7 +9650,7 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="G39" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H39" s="7" t="s">
         <x:v>329</x:v>
@@ -9698,7 +9698,7 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="G40" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H40" s="7" t="s">
         <x:v>335</x:v>
@@ -9746,7 +9746,7 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="G41" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H41" s="7" t="s">
         <x:v>341</x:v>
@@ -9794,7 +9794,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="G42" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H42" s="7" t="s">
         <x:v>347</x:v>
@@ -9816,7 +9816,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="N42" s="7" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="O42" s="12" t="s">
         <x:v>103</x:v>
@@ -9833,7 +9833,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="D43" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E43" s="7" t="s">
         <x:v>350</x:v>
@@ -9938,7 +9938,7 @@
         <x:v>363</x:v>
       </x:c>
       <x:c r="G45" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H45" s="7" t="s">
         <x:v>163</x:v>
@@ -9989,7 +9989,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="H46" s="7" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I46" s="47">
         <x:v>1</x:v>
@@ -10080,10 +10080,10 @@
         <x:v>376</x:v>
       </x:c>
       <x:c r="G48" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H48" s="7" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I48" s="47">
         <x:v>1</x:v>
@@ -10128,7 +10128,7 @@
         <x:v>381</x:v>
       </x:c>
       <x:c r="G49" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H49" s="7" t="s">
         <x:v>341</x:v>
@@ -10176,7 +10176,7 @@
         <x:v>385</x:v>
       </x:c>
       <x:c r="G50" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H50" s="7" t="s">
         <x:v>386</x:v>
@@ -10224,7 +10224,7 @@
         <x:v>391</x:v>
       </x:c>
       <x:c r="G51" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H51" s="7" t="s">
         <x:v>392</x:v>
@@ -10272,7 +10272,7 @@
         <x:v>396</x:v>
       </x:c>
       <x:c r="G52" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H52" s="7" t="s">
         <x:v>397</x:v>
@@ -10323,7 +10323,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="H53" s="7" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I53" s="47">
         <x:v>1</x:v>
@@ -10359,7 +10359,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="D54" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E54" s="7" t="s">
         <x:v>406</x:v>
@@ -10371,7 +10371,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="H54" s="7" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I54" s="47">
         <x:v>1</x:v>
@@ -10419,7 +10419,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="H55" s="7" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I55" s="47">
         <x:v>1</x:v>
@@ -10738,7 +10738,7 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="G62" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H62" s="7" t="s">
         <x:v>436</x:v>
@@ -10786,7 +10786,7 @@
         <x:v>444</x:v>
       </x:c>
       <x:c r="G63" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H63" s="7" t="s">
         <x:v>436</x:v>
@@ -10834,7 +10834,7 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="G64" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H64" s="7" t="s">
         <x:v>347</x:v>
@@ -10873,7 +10873,7 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="D65" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E65" s="7" t="s">
         <x:v>451</x:v>
@@ -10919,7 +10919,7 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="D66" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E66" s="7" t="s">
         <x:v>455</x:v>
@@ -11020,7 +11020,7 @@
         <x:v>463</x:v>
       </x:c>
       <x:c r="G68" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H68" s="7" t="s">
         <x:v>464</x:v>
@@ -11292,7 +11292,7 @@
         <x:v>486</x:v>
       </x:c>
       <x:c r="G74" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H74" s="7" t="s">
         <x:v>290</x:v>
@@ -11338,7 +11338,7 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="G75" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H75" s="7" t="s">
         <x:v>312</x:v>
@@ -11384,7 +11384,7 @@
         <x:v>492</x:v>
       </x:c>
       <x:c r="G76" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H76" s="7" t="s">
         <x:v>397</x:v>
@@ -11430,7 +11430,7 @@
         <x:v>495</x:v>
       </x:c>
       <x:c r="G77" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H77" s="7" t="s">
         <x:v>496</x:v>
@@ -11476,7 +11476,7 @@
         <x:v>499</x:v>
       </x:c>
       <x:c r="G78" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H78" s="7" t="s">
         <x:v>290</x:v>
@@ -11513,7 +11513,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="D79" s="7" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E79" s="7" t="s">
         <x:v>501</x:v>
@@ -11522,7 +11522,7 @@
         <x:v>502</x:v>
       </x:c>
       <x:c r="G79" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H79" s="7" t="s">
         <x:v>280</x:v>
@@ -11559,7 +11559,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="D80" s="7" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E80" s="7" t="s">
         <x:v>504</x:v>
@@ -11568,10 +11568,10 @@
         <x:v>505</x:v>
       </x:c>
       <x:c r="G80" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H80" s="7" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I80" s="47">
         <x:v>0</x:v>
@@ -11603,7 +11603,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="D81" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E81" s="7" t="s">
         <x:v>507</x:v>
@@ -11612,7 +11612,7 @@
         <x:v>508</x:v>
       </x:c>
       <x:c r="G81" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H81" s="7" t="s">
         <x:v>453</x:v>
@@ -11649,7 +11649,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="D82" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E82" s="7" t="s">
         <x:v>510</x:v>
@@ -11748,7 +11748,7 @@
         <x:v>517</x:v>
       </x:c>
       <x:c r="G84" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H84" s="7" t="s">
         <x:v>326</x:v>
@@ -11974,7 +11974,7 @@
         <x:v>533</x:v>
       </x:c>
       <x:c r="G89" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H89" s="7" t="s">
         <x:v>534</x:v>
@@ -12022,7 +12022,7 @@
         <x:v>538</x:v>
       </x:c>
       <x:c r="G90" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H90" s="7" t="s">
         <x:v>539</x:v>
@@ -12059,7 +12059,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="D91" s="7" t="s">
-        <x:v>272</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E91" s="7" t="s">
         <x:v>541</x:v>
@@ -12068,7 +12068,7 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="G91" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H91" s="7" t="s">
         <x:v>174</x:v>
@@ -12114,7 +12114,7 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="G92" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H92" s="7" t="s">
         <x:v>546</x:v>
@@ -12151,7 +12151,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="D93" s="7" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E93" s="7" t="s">
         <x:v>548</x:v>
@@ -12160,7 +12160,7 @@
         <x:v>549</x:v>
       </x:c>
       <x:c r="G93" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H93" s="7" t="s">
         <x:v>550</x:v>
@@ -12199,7 +12199,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="D94" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E94" s="7" t="s">
         <x:v>553</x:v>
@@ -12252,7 +12252,7 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="G95" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H95" s="7" t="s">
         <x:v>163</x:v>
@@ -12524,7 +12524,7 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="G101" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H101" s="7" t="s">
         <x:v>163</x:v>
@@ -12570,7 +12570,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="G102" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H102" s="7" t="s">
         <x:v>163</x:v>
@@ -12607,7 +12607,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="D103" s="7" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E103" s="7" t="s">
         <x:v>583</x:v>
@@ -12616,7 +12616,7 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="G103" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H103" s="7" t="s">
         <x:v>163</x:v>
@@ -12653,7 +12653,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="D104" s="7" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E104" s="7" t="s">
         <x:v>586</x:v>
@@ -12662,7 +12662,7 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="G104" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H104" s="7" t="s">
         <x:v>588</x:v>
@@ -12699,7 +12699,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="D105" s="7" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E105" s="7" t="s">
         <x:v>590</x:v>
@@ -12708,7 +12708,7 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="G105" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H105" s="7" t="s">
         <x:v>592</x:v>
@@ -12743,7 +12743,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="D106" s="7" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E106" s="7" t="s">
         <x:v>594</x:v>
@@ -12752,7 +12752,7 @@
         <x:v>595</x:v>
       </x:c>
       <x:c r="G106" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H106" s="7" t="s">
         <x:v>329</x:v>
@@ -12796,7 +12796,7 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="G107" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H107" s="7" t="s">
         <x:v>600</x:v>
@@ -13066,7 +13066,7 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="G113" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H113" s="7" t="s">
         <x:v>496</x:v>
@@ -13110,7 +13110,7 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="G114" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H114" s="7" t="s">
         <x:v>335</x:v>
@@ -13154,7 +13154,7 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="G115" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H115" s="7" t="s">
         <x:v>496</x:v>
@@ -13198,7 +13198,7 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="G116" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H116" s="7" t="s">
         <x:v>306</x:v>
@@ -13242,7 +13242,7 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="G117" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H117" s="7" t="s">
         <x:v>635</x:v>
@@ -13277,7 +13277,7 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="D118" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E118" s="7" t="s">
         <x:v>637</x:v>
@@ -13506,7 +13506,7 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="G123" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H123" s="7" t="s">
         <x:v>650</x:v>
@@ -13550,7 +13550,7 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="G124" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H124" s="7" t="s">
         <x:v>650</x:v>
@@ -13594,7 +13594,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="G125" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H125" s="7" t="s">
         <x:v>329</x:v>
@@ -13682,7 +13682,7 @@
         <x:v>671</x:v>
       </x:c>
       <x:c r="G127" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H127" s="7" t="s">
         <x:v>306</x:v>
@@ -13726,7 +13726,7 @@
         <x:v>675</x:v>
       </x:c>
       <x:c r="G128" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H128" s="7" t="s">
         <x:v>397</x:v>
@@ -13761,7 +13761,7 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="D129" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E129" s="7" t="s">
         <x:v>677</x:v>
@@ -13902,7 +13902,7 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="G132" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H132" s="7" t="s">
         <x:v>685</x:v>
@@ -13946,7 +13946,7 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="G133" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H133" s="7" t="s">
         <x:v>694</x:v>
@@ -13990,7 +13990,7 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="G134" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H134" s="7" t="s">
         <x:v>306</x:v>
@@ -14034,7 +14034,7 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="G135" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H135" s="7" t="s">
         <x:v>685</x:v>
@@ -14078,7 +14078,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="G136" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H136" s="7" t="s">
         <x:v>163</x:v>
@@ -14122,7 +14122,7 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="G137" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H137" s="7" t="s">
         <x:v>329</x:v>
@@ -14157,7 +14157,7 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="D138" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E138" s="7" t="s">
         <x:v>710</x:v>
@@ -14210,7 +14210,7 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="G139" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H139" s="7" t="s">
         <x:v>635</x:v>
@@ -14432,7 +14432,7 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="G144" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H144" s="7" t="s">
         <x:v>392</x:v>
@@ -14476,7 +14476,7 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="G145" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H145" s="7" t="s">
         <x:v>358</x:v>
@@ -14520,7 +14520,7 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="G146" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H146" s="7" t="s">
         <x:v>738</x:v>
@@ -14652,7 +14652,7 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="G149" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H149" s="7" t="s">
         <x:v>335</x:v>
@@ -14920,7 +14920,7 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="G155" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H155" s="7" t="s">
         <x:v>496</x:v>
@@ -15142,7 +15142,7 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="G160" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H160" s="7" t="s">
         <x:v>163</x:v>
@@ -15318,7 +15318,7 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="G164" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H164" s="7" t="s">
         <x:v>317</x:v>
@@ -15362,7 +15362,7 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="G165" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H165" s="7" t="s">
         <x:v>738</x:v>
@@ -15406,7 +15406,7 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="G166" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H166" s="7" t="s">
         <x:v>453</x:v>
@@ -15714,7 +15714,7 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="G173" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H173" s="7" t="s">
         <x:v>835</x:v>
@@ -15758,7 +15758,7 @@
         <x:v>841</x:v>
       </x:c>
       <x:c r="G174" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H174" s="7" t="s">
         <x:v>358</x:v>
@@ -15802,7 +15802,7 @@
         <x:v>844</x:v>
       </x:c>
       <x:c r="G175" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H175" s="7" t="s">
         <x:v>845</x:v>
@@ -15846,7 +15846,7 @@
         <x:v>848</x:v>
       </x:c>
       <x:c r="G176" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H176" s="7" t="s">
         <x:v>849</x:v>
@@ -15890,7 +15890,7 @@
         <x:v>853</x:v>
       </x:c>
       <x:c r="G177" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H177" s="7" t="s">
         <x:v>358</x:v>
@@ -15934,7 +15934,7 @@
         <x:v>857</x:v>
       </x:c>
       <x:c r="G178" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H178" s="7" t="s">
         <x:v>358</x:v>
@@ -15978,7 +15978,7 @@
         <x:v>860</x:v>
       </x:c>
       <x:c r="G179" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H179" s="7" t="s">
         <x:v>358</x:v>
@@ -16057,7 +16057,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="D181" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E181" s="7" t="s">
         <x:v>865</x:v>
@@ -16242,7 +16242,7 @@
         <x:v>879</x:v>
       </x:c>
       <x:c r="G185" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H185" s="7" t="s">
         <x:v>358</x:v>
@@ -16418,7 +16418,7 @@
         <x:v>893</x:v>
       </x:c>
       <x:c r="G189" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H189" s="7" t="s">
         <x:v>721</x:v>
@@ -16462,7 +16462,7 @@
         <x:v>896</x:v>
       </x:c>
       <x:c r="G190" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H190" s="7" t="s">
         <x:v>550</x:v>
@@ -16497,7 +16497,7 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="D191" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E191" s="7" t="s">
         <x:v>898</x:v>
@@ -16770,7 +16770,7 @@
         <x:v>919</x:v>
       </x:c>
       <x:c r="G197" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H197" s="7" t="s">
         <x:v>317</x:v>
@@ -16814,7 +16814,7 @@
         <x:v>922</x:v>
       </x:c>
       <x:c r="G198" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H198" s="7" t="s">
         <x:v>317</x:v>
@@ -16858,7 +16858,7 @@
         <x:v>926</x:v>
       </x:c>
       <x:c r="G199" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H199" s="7" t="s">
         <x:v>280</x:v>
@@ -16946,7 +16946,7 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="G201" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H201" s="7" t="s">
         <x:v>835</x:v>
@@ -16990,7 +16990,7 @@
         <x:v>937</x:v>
       </x:c>
       <x:c r="G202" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H202" s="7" t="s">
         <x:v>317</x:v>
@@ -17025,7 +17025,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="D203" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E203" s="7" t="s">
         <x:v>939</x:v>
@@ -17254,7 +17254,7 @@
         <x:v>957</x:v>
       </x:c>
       <x:c r="G208" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H208" s="7" t="s">
         <x:v>782</x:v>
@@ -17298,7 +17298,7 @@
         <x:v>960</x:v>
       </x:c>
       <x:c r="G209" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H209" s="7" t="s">
         <x:v>782</x:v>
@@ -17342,7 +17342,7 @@
         <x:v>963</x:v>
       </x:c>
       <x:c r="G210" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H210" s="7" t="s">
         <x:v>782</x:v>
@@ -17430,7 +17430,7 @@
         <x:v>970</x:v>
       </x:c>
       <x:c r="G212" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H212" s="7" t="s">
         <x:v>650</x:v>
@@ -17832,10 +17832,10 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="G221" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H221" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="I221" s="47">
         <x:v>3</x:v>
@@ -17876,7 +17876,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="G222" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H222" s="7" t="s">
         <x:v>329</x:v>
@@ -17920,7 +17920,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="G223" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H223" s="7" t="s">
         <x:v>280</x:v>
@@ -17964,7 +17964,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="G224" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H224" s="7" t="s">
         <x:v>1012</x:v>
@@ -18008,7 +18008,7 @@
         <x:v>1015</x:v>
       </x:c>
       <x:c r="G225" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H225" s="7" t="s">
         <x:v>635</x:v>
@@ -18045,7 +18045,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="D226" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E226" s="7" t="s">
         <x:v>1018</x:v>
@@ -18318,7 +18318,7 @@
         <x:v>1039</x:v>
       </x:c>
       <x:c r="G232" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H232" s="7" t="s">
         <x:v>756</x:v>
@@ -18406,7 +18406,7 @@
         <x:v>1047</x:v>
       </x:c>
       <x:c r="G234" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H234" s="7" t="s">
         <x:v>756</x:v>
@@ -18450,7 +18450,7 @@
         <x:v>1050</x:v>
       </x:c>
       <x:c r="G235" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H235" s="7" t="s">
         <x:v>397</x:v>
@@ -18538,7 +18538,7 @@
         <x:v>1058</x:v>
       </x:c>
       <x:c r="G237" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H237" s="7" t="s">
         <x:v>635</x:v>
@@ -18760,7 +18760,7 @@
         <x:v>1078</x:v>
       </x:c>
       <x:c r="G242" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H242" s="7" t="s">
         <x:v>1074</x:v>
@@ -18804,7 +18804,7 @@
         <x:v>1081</x:v>
       </x:c>
       <x:c r="G243" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H243" s="7" t="s">
         <x:v>1074</x:v>
@@ -18848,7 +18848,7 @@
         <x:v>1085</x:v>
       </x:c>
       <x:c r="G244" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H244" s="7" t="s">
         <x:v>436</x:v>
@@ -18892,7 +18892,7 @@
         <x:v>1089</x:v>
       </x:c>
       <x:c r="G245" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H245" s="7" t="s">
         <x:v>1024</x:v>
@@ -18936,7 +18936,7 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="G246" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H246" s="7" t="s">
         <x:v>643</x:v>
@@ -19024,7 +19024,7 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="G248" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H248" s="7" t="s">
         <x:v>1101</x:v>
@@ -19200,7 +19200,7 @@
         <x:v>1114</x:v>
       </x:c>
       <x:c r="G252" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H252" s="7" t="s">
         <x:v>643</x:v>
@@ -19244,7 +19244,7 @@
         <x:v>1117</x:v>
       </x:c>
       <x:c r="G253" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H253" s="7" t="s">
         <x:v>643</x:v>
@@ -19288,7 +19288,7 @@
         <x:v>1120</x:v>
       </x:c>
       <x:c r="G254" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H254" s="7" t="s">
         <x:v>643</x:v>
@@ -19332,7 +19332,7 @@
         <x:v>1123</x:v>
       </x:c>
       <x:c r="G255" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H255" s="7" t="s">
         <x:v>643</x:v>
@@ -19367,7 +19367,7 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="D256" s="7" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E256" s="7" t="s">
         <x:v>1125</x:v>
@@ -19376,7 +19376,7 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="G256" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H256" s="7" t="s">
         <x:v>1127</x:v>
@@ -19411,7 +19411,7 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="D257" s="7" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E257" s="7" t="s">
         <x:v>1129</x:v>
@@ -19420,7 +19420,7 @@
         <x:v>1130</x:v>
       </x:c>
       <x:c r="G257" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H257" s="7" t="s">
         <x:v>358</x:v>
@@ -19455,7 +19455,7 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="D258" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E258" s="7" t="s">
         <x:v>1132</x:v>
@@ -19829,7 +19829,7 @@
       </x:c>
       <x:c r="E10" s="7" t="str">
         <x:f>'Catalogo Maestro'!G10</x:f>
-        <x:v>Base incluido</x:v>
+        <x:v>Opcional</x:v>
       </x:c>
       <x:c r="F10" s="16" t="n">
         <x:f>'Catalogo Maestro'!J10</x:f>
@@ -19867,7 +19867,7 @@
       </x:c>
       <x:c r="E11" s="7" t="str">
         <x:f>'Catalogo Maestro'!G11</x:f>
-        <x:v>Base incluido</x:v>
+        <x:v>Opcional</x:v>
       </x:c>
       <x:c r="F11" s="16" t="n">
         <x:f>'Catalogo Maestro'!J11</x:f>
@@ -20247,7 +20247,7 @@
       </x:c>
       <x:c r="E21" s="7" t="str">
         <x:f>'Catalogo Maestro'!G21</x:f>
-        <x:v>Base incluido</x:v>
+        <x:v>Base obligatorio</x:v>
       </x:c>
       <x:c r="F21" s="16" t="n">
         <x:f>'Catalogo Maestro'!J21</x:f>
@@ -20323,7 +20323,7 @@
       </x:c>
       <x:c r="E23" s="7" t="str">
         <x:f>'Catalogo Maestro'!G23</x:f>
-        <x:v>Base incluido</x:v>
+        <x:v>Opcional</x:v>
       </x:c>
       <x:c r="F23" s="16" t="n">
         <x:f>'Catalogo Maestro'!J23</x:f>
@@ -20361,7 +20361,7 @@
       </x:c>
       <x:c r="E24" s="7" t="str">
         <x:f>'Catalogo Maestro'!G24</x:f>
-        <x:v>Base incluido</x:v>
+        <x:v>Opcional</x:v>
       </x:c>
       <x:c r="F24" s="16" t="n">
         <x:f>'Catalogo Maestro'!J24</x:f>
